--- a/output/graficos_nacionales/plot_nacional_o_ocup_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_o_ocup_a_2022.xlsx
@@ -15405,7 +15405,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tasa de ocupación formal dependiente</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_o_ocup_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_o_ocup_a_2022.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="699">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Macrozona Austral</t>
   </si>
   <si>
-    <t xml:space="preserve">value</t>
+    <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
     <t xml:space="preserve">12301</t>
@@ -1567,18 +1567,18 @@
     <t xml:space="preserve">Renaico</t>
   </si>
   <si>
+    <t xml:space="preserve">9201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angol</t>
+  </si>
+  <si>
     <t xml:space="preserve">10203</t>
   </si>
   <si>
     <t xml:space="preserve">Chonchi</t>
   </si>
   <si>
-    <t xml:space="preserve">9201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angol</t>
-  </si>
-  <si>
     <t xml:space="preserve">10105</t>
   </si>
   <si>
@@ -1654,18 +1654,18 @@
     <t xml:space="preserve">Padre Las Casas</t>
   </si>
   <si>
+    <t xml:space="preserve">14106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mariquina</t>
+  </si>
+  <si>
     <t xml:space="preserve">10307</t>
   </si>
   <si>
     <t xml:space="preserve">San Pablo</t>
   </si>
   <si>
-    <t xml:space="preserve">14106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mariquina</t>
-  </si>
-  <si>
     <t xml:space="preserve">14105</t>
   </si>
   <si>
@@ -1684,18 +1684,18 @@
     <t xml:space="preserve">Río Negro</t>
   </si>
   <si>
+    <t xml:space="preserve">8312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tucapel</t>
+  </si>
+  <si>
     <t xml:space="preserve">10102</t>
   </si>
   <si>
     <t xml:space="preserve">Calbuco</t>
   </si>
   <si>
-    <t xml:space="preserve">8312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tucapel</t>
-  </si>
-  <si>
     <t xml:space="preserve">14201</t>
   </si>
   <si>
@@ -2068,7 +2068,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:26</t>
+    <t xml:space="preserve">2026-09-07 13:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2080,16 +2080,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_nacional_o_ocup_a_2022.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Tasa de ocupacion formal dependiente</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Comuna (vista nacional macrozonal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -10262,10 +10271,10 @@
         <v>2022</v>
       </c>
       <c r="B244" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>464</v>
+        <v>494</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>516</v>
@@ -10294,10 +10303,10 @@
         <v>2022</v>
       </c>
       <c r="B245" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>494</v>
+        <v>464</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>518</v>
@@ -10742,10 +10751,10 @@
         <v>2022</v>
       </c>
       <c r="B259" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>464</v>
+        <v>501</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>545</v>
@@ -10774,10 +10783,10 @@
         <v>2022</v>
       </c>
       <c r="B260" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>501</v>
+        <v>464</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>547</v>
@@ -10902,10 +10911,10 @@
         <v>2022</v>
       </c>
       <c r="B264" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>555</v>
@@ -10934,10 +10943,10 @@
         <v>2022</v>
       </c>
       <c r="B265" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>557</v>
@@ -12966,23 +12975,23 @@
         <v>688</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
     </row>
   </sheetData>
@@ -12997,28 +13006,28 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13027,7 +13036,7 @@
         <v>2022</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_o_ocup_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_o_ocup_a_2022.xlsx
@@ -2068,7 +2068,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 13:08</t>
+    <t xml:space="preserve">2026-09-08 10:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
